--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92553433721</v>
+        <v>46157.93107319217</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93107319217</v>
+        <v>46157.93132267365</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93132267365</v>
+        <v>46157.93380304922</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93380304922</v>
+        <v>46157.93690891637</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93690891637</v>
+        <v>46158.28203237188</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28203237188</v>
+        <v>46158.29734430578</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29734430578</v>
+        <v>46158.2980348374</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2980348374</v>
+        <v>46158.33367142646</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33367142646</v>
+        <v>46158.37218989839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.9_Прочее_процессуальное/ПОЯСНИТЕЛЬНАЯ ЗАПИСКА 1/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37218989839</v>
+        <v>46158.37273798993</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
